--- a/research/brics_universities/output/BRICS_universities_iran.xlsx
+++ b/research/brics_universities/output/BRICS_universities_iran.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AI$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Иран'!$A$1:$AI$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Иран'!$A$1:$AI$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
@@ -547,13 +547,13 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
       </c>
       <c r="H5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -983,9 +983,10 @@
         <is>
           <t>• САНКЦИИ: организация включена в список OFAC SDN (запись 27325, программы NPWMD/IFSR; обозначена Минфином США в сентябре 2019 г.). По Википедии — также под санкциями Великобритании, Канады и Новой Зеландии, но в текущей выгрузке UK Sanctions List по названию не найдена. Очень высокий санкционный риск — контакт только после юридической проверки
 • По сообщениям (Википедия, со ссылкой на The Washington Times), штаб-квартира ISRC в центре Тегерана была поражена израильским ударом 13–16 марта 2026 г. в ходе войны 2026 г
-• Официальный сайт isrc.ac.ir недоступен (ошибка 504) — адрес, телефон, e-mail и руководитель не подтверждены. По Википедии и.о. руководителя с 2022 г. — Хасан Саларие (одновременно глава Иранского космического агентства); актуальность на 2025–2026 гг. не подтверждена
+• Официальный сайт isrc.ac.ir недоступен (ошибка 504, повторно 04.10.2026) — адрес, телефон, e-mail и руководитель не подтверждены. По Википедии и.о. руководителя с 2022 г. — Хасан Саларие (одновременно глава Иранского космического агентства); актуальность на 2025–2026 гг. не подтверждена
 • Спутники: Pars-1 и Nahid-2 — подрядчик ISRC (Gunter's Space Page), запуски на Союз-2.1б с Восточного; Mahda (запуск на «Симорге», 2024) — по Википедии. Nahid-1 потерян при неудачном пуске Qaem-100 04.03.2023
-• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки</t>
+• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки
+• Перепроверка: Сайт isrc.ac.ir недоступен (504 Gateway Timeout, в т.ч. через reader-сервис, 04.10.2026); данные не изменены</t>
         </is>
       </c>
       <c r="AG2" s="4" t="inlineStr">
@@ -1719,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI85"/>
+  <dimension ref="A1:AI84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2058,9 +2059,10 @@
         <is>
           <t>• САНКЦИИ: организация включена в список OFAC SDN (запись 27325, программы NPWMD/IFSR; обозначена Минфином США в сентябре 2019 г.). По Википедии — также под санкциями Великобритании, Канады и Новой Зеландии, но в текущей выгрузке UK Sanctions List по названию не найдена. Очень высокий санкционный риск — контакт только после юридической проверки
 • По сообщениям (Википедия, со ссылкой на The Washington Times), штаб-квартира ISRC в центре Тегерана была поражена израильским ударом 13–16 марта 2026 г. в ходе войны 2026 г
-• Официальный сайт isrc.ac.ir недоступен (ошибка 504) — адрес, телефон, e-mail и руководитель не подтверждены. По Википедии и.о. руководителя с 2022 г. — Хасан Саларие (одновременно глава Иранского космического агентства); актуальность на 2025–2026 гг. не подтверждена
+• Официальный сайт isrc.ac.ir недоступен (ошибка 504, повторно 04.10.2026) — адрес, телефон, e-mail и руководитель не подтверждены. По Википедии и.о. руководителя с 2022 г. — Хасан Саларие (одновременно глава Иранского космического агентства); актуальность на 2025–2026 гг. не подтверждена
 • Спутники: Pars-1 и Nahid-2 — подрядчик ISRC (Gunter's Space Page), запуски на Союз-2.1б с Восточного; Mahda (запуск на «Симорге», 2024) — по Википедии. Nahid-1 потерян при неудачном пуске Qaem-100 04.03.2023
-• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки</t>
+• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки
+• Перепроверка: Сайт isrc.ac.ir недоступен (504 Gateway Timeout, в т.ч. через reader-сервис, 04.10.2026); данные не изменены</t>
         </is>
       </c>
       <c r="AG2" s="4" t="inlineStr">
@@ -5036,7 +5038,8 @@
           <t>• Официальные сайты sums.ac.ir и gsia.sums.ac.ir недоступны из нашей сети (блокировка/403) — контакты не проверены, e-mail и телефон оставлены пустыми
 • Президент Seyed Basir Hashemi указан по en/fa-Википедии (обе совпадают), на официальном сайте не подтверждён — проверить перед рассылкой
 • Адрес — по профилю THE (Zand Blvd, 71348-1433)
-• Медицинский вуз; спутников не ожидается, отдельная проверка не проводилась (исчерпан лимит поиска)</t>
+• Медицинский вуз; спутников не ожидается, отдельная проверка не проводилась (исчерпан лимит поиска)
+• Перепроверка: 04.10.2026: sums.ac.ir по-прежнему недоступен из-за пределов Ирана (прокси и WebFetch — 503); данные не изменены</t>
         </is>
       </c>
       <c r="AG21" s="4" t="inlineStr">
@@ -5773,7 +5776,8 @@
 • Президент Shoja Ahmadvand — по англ. и фа-Википедии; дата назначения в источниках не указана, официально не подтверждено
 • Гуманитарный профиль (экономика, право, менеджмент) — для CubeSat-проекта релевантен разве что в части космического права/политики
 • Телефон +98 21 4839 0000 — по uniRank (вторичный источник). E-mail не найдены
-• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0</t>
+• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0
+• Перепроверка: 04.10.2026: atu.ac.ir / en.atu.ac.ir по-прежнему недоступны (503 / нет соединения); данные не изменены</t>
         </is>
       </c>
       <c r="AG26" s="4" t="inlineStr">
@@ -6196,7 +6200,8 @@
           <t>• Персидский сайт azaruniv.ac.ir недоступен (таймаут); английский сайт устаревший (контакты — только веб-форма, обращение ректора без имени). Руководитель, e-mail и телефон не подтверждены; в Википедии — Мохаммад Багер Мохаммад Садеги Азад (вероятно устарело)
 • Адрес взят из Википедии, официальной страницей не подтверждён. Офис международного сотрудничества: http://en.azaruniv.ac.ir/?PageID=137 (не открылся)
 • Космическая проверка (LIGHT) — только по nanosats.csv/Gunter's Space Page: спутников не найдено (лимит веб-поиска исчерпан, отдельный поиск не выполнялся)
-• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки</t>
+• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки
+• Перепроверка: Сайты azaruniv.ac.ir и en.azaruniv.ac.ir недоступны (таймаут через прокси и reader-сервис, 04.10.2026); данные не изменены</t>
         </is>
       </c>
       <c r="AG29" s="4" t="inlineStr">
@@ -6779,7 +6784,8 @@
 • Президент Dr. Abolghasem Khazaeian — по фа-Википедии (с 30.11.1403, февраль 2025); англ. Википедия (Dr. Shaban Shataee Jouybari) устарела. Официально не подтверждено
 • Телефон в uniRank/Википедии в старом формате (0171-222 0028 / 0171-2220320) — номер в новом 8-значном формате не подтверждён, поэтому поле phone пустое. E-mail не найдены
 • Для проекта VLEO-CubeSat интересен как потенциальный пользователь данных ДЗЗ (лесное хозяйство, водосборы)
-• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0</t>
+• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0
+• Перепроверка: Сайт gau.ac.ir недоступен (503 / сброс соединения) — данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG33" s="4" t="inlineStr">
@@ -7047,7 +7053,8 @@
 • Быстрая проверка спутников: не найдено
 • Иран под всеобъемлющими санкциями США (ITSR/OFAC) и ограничительными мерами ЕС/Великобритании; перед контактом нужна юридическая/комплаенс-проверка
 • Санкционная проверка (кэш CSL США/SDN, ЕС, UK от 04.10.2026): университет не найден; restricted_list пуст
-• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой</t>
+• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой
+• Перепроверка: Сайт ilam.ac.ir недоступен (04.10.2026, все варианты); официальный Telegram-канал не найден; данные не изменены</t>
         </is>
       </c>
       <c r="AG35" s="4" t="inlineStr">
@@ -7168,17 +7175,19 @@
       <c r="AF36" s="4" t="inlineStr">
         <is>
           <t>• САНКЦИИ: В загруженных списках (US CSL/Entity List, OFAC SDN, EU consolidated, UK Sanctions List, версии на 10.2026) университет как организация НЕ найден; общий страновой санкционный режим в отношении Ирана сохраняется — требуется комплаенс-проверка до отправки приглашения
-• Официальный сайт недоступен из-за пределов Ирана (таймаут/сброс соединения, в т.ч. через зеркало r.jina.ai); данные взяты из Википедии и uniRank — вторичные источники, требуют перепроверки
-• Президент Dr. Hamid Taheri — по фа-Википедии (с мая 2025 г.); ссылка в Википедии не подтверждает дату. Требует перепроверки
-• Телефон uniRank в старом формате ((281) 378 0021) — не используется. E-mail не найдены
-• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0</t>
+• Официальный сайт недоступен из-за пределов Ирана (таймаут/сброс соединения, повторно 04.10.2026); адрес — из вторичных источников (Википедия, uniRank)
+• Президент Dr. Hamid Taheri (д-р персидской литературы): и.о. с 30.04.2025, утверждён Высшим советом культурной революции 03.08.2025; действующий по официальному Telegram-каналу @ikiu_ac (посты 20–27.09.2026)
+• Телефон uniRank в старом формате ((281) 378 0021) — не используется. Общий/международный e-mail не найден (в Telegram-канале только адреса фестивалей: festival.intl@pst.ikiu.ac.ir)
+• Быстрая проверка спутников: в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0
+• Перепроверка: Президент д-р Хамид Тахери подтверждён официальным Telegram-каналом IKIU (сентябрь 2026; утверждён ВСКР 03.08.2025); сайт по-прежнему недоступен — e-mail и телефон не найдены</t>
         </is>
       </c>
       <c r="AG36" s="4" t="inlineStr">
         <is>
           <t>• Https://fa.wikipedia.org/wiki/دانشگاه_بین‌المللی_امام_خمینی
 • Https://en.wikipedia.org/wiki/Imam_Khomeini_International_University
-• Https://www.unirank.org/ir/uni/imam-khomeini-international-university/</t>
+• Https://www.unirank.org/ir/uni/imam-khomeini-international-university/
+• Https://t.me/s/ikiu_ac</t>
         </is>
       </c>
       <c r="AH36" s="4" t="inlineStr">
@@ -7444,7 +7453,8 @@
 • Сеть из десятков филиалов по всему Ирану (и за рубежом) с центральной организацией в Тегеране; адрес центрального аппарата, телефоны и e-mail получить не удалось — сайты iau.ir / iau.ac.ir / intl.iau.ir недоступны (ошибка HTTP/3)
 • Президент Bijan Ranjbar избран Советом попечителей 06.10.2025 (агентство ANA)
 • Для приглашения, вероятно, разумнее адресоваться к конкретному филиалу с инженерным/аэрокосмическим профилем (например, Science and Research Branch, Тегеран) — не проверено
-• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0</t>
+• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0
+• Перепроверка: Сайты iau.ir / iau.ac.ir по-прежнему недоступны (04.10.2026, сброс соединения); сайт MSRT также недоступен; данные не изменены</t>
         </is>
       </c>
       <c r="AG38" s="4" t="inlineStr">
@@ -7854,7 +7864,9 @@
 • Открытый (дистанционный) государственный университет с сетью центров по всей стране; штаб-квартира в Тегеране (по Wikipedia)
 • По Wikipedia президент — Мохаммад Хади Амин Наджи; актуальность не подтверждена
 • Космических проектов не выявлено (проверка только по nanosats.csv — квота веб-поиска исчерпана)
-• В санкционных списках ЕС/UK/США не найден; общие санкции против Ирана — нужна комплаенс-проверка</t>
+• В санкционных списках ЕС/UK/США не найден; общие санкции против Ирана — нужна комплаенс-проверка
+• Повторный поиск (10.2026) даёт противоречивые сведения о руководителе (Амин Наджи / Али Пулади Ришехри) — поле руководителя оставлено пустым
+• Перепроверка: 04.10.2026: pnu.ac.ir недоступен (сброс соединения); руководитель не подтверждён — данные не изменены</t>
         </is>
       </c>
       <c r="AG41" s="4" t="inlineStr">
@@ -8276,7 +8288,8 @@
 • Быстрая проверка спутников: не найдено
 • Иран под всеобъемлющими санкциями США (ITSR/OFAC) и ограничительными мерами ЕС/Великобритании; перед контактом нужна юридическая/комплаенс-проверка
 • Санкционная проверка (кэш CSL США/SDN, ЕС, UK от 04.10.2026): университет не найден; restricted_list пуст
-• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой</t>
+• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой
+• Перепроверка: Сайты *.ac.ir (sut.ac.ir, en.sut.ac.ir, msrt.ir) по-прежнему недоступны 04.10.2026; данные не изменены</t>
         </is>
       </c>
       <c r="AG44" s="4" t="inlineStr">
@@ -9023,7 +9036,8 @@
 • Быстрая проверка спутников: не найдено
 • Иран под всеобъемлющими санкциями США (ITSR/OFAC) и ограничительными мерами ЕС/Великобритании; перед контактом нужна юридическая/комплаенс-проверка
 • Санкционная проверка (кэш CSL США/SDN, ЕС, UK от 04.10.2026): университет не найден; restricted_list пуст
-• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой</t>
+• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой
+• Перепроверка: Сайт sku.ac.ir (http/https, en.) недоступен (503 / сброс соединения) — данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG49" s="4" t="inlineStr">
@@ -9214,7 +9228,11 @@
           <t>https://guilan.ac.ir</t>
         </is>
       </c>
-      <c r="P51" s="4" t="inlineStr"/>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Ali Basti (علی باستی)</t>
+        </is>
+      </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
           <t>President</t>
@@ -9252,16 +9270,19 @@
       </c>
       <c r="AF51" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт недоступен из нашей сети (таймаут/503 через прокси и reader), квота веб-поиска исчерпана — контакты и руководитель не проверены; заполнить вручную
-• По Wikipedia (en/fa) президент — Али Басти; актуальность на 2025–2026 не подтверждена
-• Космических проектов не выявлено (проверка только по nanosats.csv — квота веб-поиска исчерпана)
-• В санкционных списках ЕС/UK/США не найден; общие санкции против Ирана — нужна комплаенс-проверка</t>
+          <t>• Официальный сайт guilan.ac.ir по-прежнему недоступен из нашей сети (таймаут/503, в т.ч. WebFetch, 04.10.2026) — контакты не проверены; заполнить вручную
+• Руководитель — Dr. Ali Basti: по поисковому индексу официальной страницы «رؤسا و معاونین» в должности с мордада 1404 (08.2025); в новостях вуза упоминается как «سرپرست» (врио) — уточнить статус (президент или исполняющий обязанности)
+• Космических проектов не выявлено (проверка только по nanosats.csv)
+• В санкционных списках ЕС/UK/США не найден; общие санкции против Ирана — нужна комплаенс-проверка
+• Перепроверка: Сайт недоступен; руководитель Али Басти внесён по поисковому индексу официальной страницы (с 08.2025, возможно врио), контакты не найдены</t>
         </is>
       </c>
       <c r="AG51" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/University_of_Guilan
 • Https://fa.wikipedia.org/wiki/دانشگاه_گیلان
+• Https://guilan.ac.ir/officials (по поисковому индексу)
+• Https://mst.guilan.ac.ir/en/web/guilan/w/fhsjd (по поисковому индексу)
 • Nanosats.csv</t>
         </is>
       </c>
@@ -9666,7 +9687,9 @@
           <t>• Страницы президента (admin.maragheh.ac.ir/presidency) и Группы научного и международного сотрудничества (int.maragheh.ac.ir) не открываются (таймаут, отозванный сертификат en.maragheh.ac.ir) — руководитель и международный e-mail не подтверждены. В Википедии указан Мохаммад Задшакуян — актуальность не проверена
 • Почтовые индексы на сайте: 5518779840 – 5518779842
 • Космическая проверка (LIGHT) — только по nanosats.csv/Gunter's Space Page: спутников не найдено (лимит веб-поиска исчерпан, отдельный поиск не выполнялся)
-• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки</t>
+• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки
+• По поисковой выдаче (страница maragheh.ac.ir/Page/3 и СМИ) руководитель — д-р Расул Маруфи-Азар (سرپرست/рئیس, доцент, мех. инженерия) — официальную страницу открыть не удалось, в head_name не внесено
+• Перепроверка: 04.10.2026: maragheh.ac.ir недоступен (сброс соединения); найдено вероятное имя руководителя (Р. Маруфи-Азар) только в поисковой выдаче — поля не изменены</t>
         </is>
       </c>
       <c r="AG54" s="4" t="inlineStr">
@@ -9788,7 +9811,8 @@
           <t>• Официальные сайты (umz.ac.ir, foreign.umz.ac.ir) недоступны из нашей сети — контакты не проверены
 • Президент не установлен: en-Википедия и таблица в fa-Википедии называют д-ра Хешматоллу Алинежада (с 2021/1400), а карточка fa-Википедии — д-ра Эбрахима Салехи Омрана; данные противоречат друг другу — уточнить
 • Адрес — по профилю THE (Pasdaran St., Babolsar, 47415)
-• Проверка на спутники не проведена (исчерпан лимит поиска); в nanosats.csv вуз отсутствует</t>
+• Проверка на спутники не проведена (исчерпан лимит поиска); в nanosats.csv вуз отсутствует
+• Перепроверка: Сайты umz.ac.ir / en.umz.ac.ir / foreign.umz.ac.ir по-прежнему недоступны (04.10.2026, сброс соединения); данные не изменены</t>
         </is>
       </c>
       <c r="AG55" s="4" t="inlineStr">
@@ -10188,7 +10212,8 @@
           <t>• Официальный сайт недоступен из нашей сети (таймаут/503 через прокси и reader), квота веб-поиска исчерпана — контакты и руководитель не проверены; заполнить вручную
 • Wikipedia противоречива: en — Gholamreza Rezaei, fa — Gholamreza Zamanian; президент не подтверждён
 • Космических проектов не выявлено (проверка только по nanosats.csv — квота веб-поиска исчерпана)
-• В санкционных списках ЕС/UK/США не найден; общие санкции против Ирана — нужна комплаенс-проверка</t>
+• В санкционных списках ЕС/UK/США не найден; общие санкции против Ирана — нужна комплаенс-проверка
+• Перепроверка: Сайт usb.ac.ir (и en.) недоступен из нашей сети (curl/WebFetch 503) 04.10.2026; данные не изменены</t>
         </is>
       </c>
       <c r="AG58" s="4" t="inlineStr">
@@ -10604,7 +10629,8 @@
 • Общего/международного e-mail на сайте нет (найден только indust@ausmt.ac.ir — отдел связей с промышленностью). Английская версия сайта (en.ausmt.ac.ir) — пустая заглушка Plesk
 • Член Союза государственных университетов и НИИ прикаспийских стран (CASPIAN union, с 2025 г., по новостям сайта)
 • Космическая проверка (LIGHT) — только по nanosats.csv/Gunter's Space Page: спутников не найдено (лимит веб-поиска исчерпан, отдельный поиск не выполнялся)
-• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки</t>
+• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки
+• Перепроверка: Сайт ausmt.ac.ir по-прежнему недоступен 04.10.2026; данные не изменены</t>
         </is>
       </c>
       <c r="AG61" s="4" t="inlineStr">
@@ -10726,10 +10752,11 @@
       </c>
       <c r="AF62" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт arakut.ac.ir не открывается (тайм-аут) — контакты не проверены
-• Fa-Википедия называет президентом Моджтабу Гударзи (без даты) — не подтверждено, поле оставлено пустым
+          <t>• Официальный сайт arakut.ac.ir (http/https, www) по-прежнему не открывается (тайм-аут, 04.10.2026) — контакты не проверены
+• Fa-Википедия и поисковая выдача называют президентом Моджтабу Гударзи (مجتبی گودرزی) без даты — не подтверждено официальным источником, поле оставлено пустым. Есть официальный канал вуза в Eitaa (eitaa.com/ArakUTofficial) — для ручной проверки
 • THE2027: только статус Reporter (без ранга). Адрес — по профилю THE (Daneshgah St., Arak)
-• Проверка на спутники не проведена (исчерпан лимит поиска); в nanosats.csv вуз отсутствует</t>
+• Проверка на спутники не проведена; в nanosats.csv вуз отсутствует
+• Перепроверка: Сайт недоступен; данные не изменены</t>
         </is>
       </c>
       <c r="AG62" s="4" t="inlineStr">
@@ -10984,11 +11011,12 @@
       <c r="AF64" s="4" t="inlineStr">
         <is>
           <t>• САНКЦИИ: В загруженных списках (US CSL/Entity List, OFAC SDN, EU consolidated, UK Sanctions List, версии на 10.2026) университет как организация НЕ найден; общий страновой санкционный режим в отношении Ирана сохраняется — требуется комплаенс-проверка до отправки приглашения
-• Официальный сайт недоступен из-за пределов Ирана (таймаут/сброс соединения, в т.ч. через зеркало r.jina.ai); данные взяты из Википедии и uniRank — вторичные источники, требуют перепроверки
-• Президент не подтверждён: в фа-Википедии указан Dr. Amir Rajaei со ссылкой на страницу сайта 2022 г. — устаревшие данные, поле head_name оставлено пустым
+• Официальный сайт cmu.ac.ir и иранские СМИ/госсайты (mehrnews, ana.ir, khwarizmi.ir) недоступны из нашей сети (таймаут/сброс соединения/503, 04.10.2026); данные — из Википедии и uniRank, требуют перепроверки
+• Президент не подтверждён: фа-Википедия и поисковая выдача называют Dr. Amir Rajaei (امیر رجائی), без надёжной даты — поле head_name оставлено пустым
 • Телефон +98 54 3532 0020 и индекс 9971756499 — по uniRank (вторичный источник). E-mail не найдены
 • Рядом строится Чабахарский космодром (National Satellite Launch Base) — возможный контекст для сотрудничества, но связь университета с ним не подтверждена
-• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0</t>
+• Быстрая проверка спутников: в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0
+• Перепроверка: Сайт и иранские источники недоступны; данные не изменены</t>
         </is>
       </c>
       <c r="AG64" s="4" t="inlineStr">
@@ -11079,7 +11107,8 @@
           <t>• САНКЦИИ: В загруженных списках (US CSL/Entity List, OFAC SDN, EU consolidated, UK Sanctions List, версии на 10.2026) университет как организация НЕ найден; общий страновой санкционный режим в отношении Ирана сохраняется — требуется комплаенс-проверка до отправки приглашения
 • Данные практически не найдены: статьи в Википедии нет, предполагаемые домены (ershad.ac.ir, edu.ershad.ac.ir) не резолвятся, web search исчерпан. Персидское название (институт высшего образования «Эршад Дамаванд») и город (Тегеран) — не подтверждены официальным источником
 • Негосударственный вуз небольшого размера, без инженерно-космического профиля (по косвенным данным) — низкий приоритет для рассылки
-• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0</t>
+• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0
+• Перепроверка: Официальный сайт по-прежнему не найден; данные не изменены</t>
         </is>
       </c>
       <c r="AG65" s="4" t="inlineStr">
@@ -11191,7 +11220,8 @@
 • Быстрая проверка спутников: не найдено
 • Иран под всеобъемлющими санкциями США (ITSR/OFAC) и ограничительными мерами ЕС/Великобритании; перед контактом нужна юридическая/комплаенс-проверка
 • Санкционная проверка (кэш CSL США/SDN, ЕС, UK от 04.10.2026): университет не найден; restricted_list пуст
-• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой</t>
+• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой
+• Перепроверка: Сайт fasau.ac.ir и mehrnews.com по-прежнему недоступны; расхождение по руководителю (Бадехиян / Зареи / Фатхоллахи) не разрешено — данные не изменены</t>
         </is>
       </c>
       <c r="AG66" s="4" t="inlineStr">
@@ -11293,7 +11323,8 @@
 • Официальный сайт недоступен из нашей сети (таймаут/503 через прокси и reader), квота веб-поиска исчерпана — контакты и руководитель не проверены; заполнить вручную
 • По Wikipedia президент — Хосейн Мохеби (ссылка на старую новость MSRT); не подтверждено
 • Космических проектов не выявлено (проверка только по nanosats.csv — квота веб-поиска исчерпана)
-• В санкционных списках ЕС/UK/США не найден; общие санкции против Ирана — нужна комплаенс-проверка</t>
+• В санкционных списках ЕС/UK/США не найден; общие санкции против Ирана — нужна комплаенс-проверка
+• Перепроверка: Сайт kgut.ac.ir (www и без www) недоступен — ERR_CONNECTION_REFUSED через reader-сервис, сброс через прокси (04.10.2026); данные не изменены</t>
         </is>
       </c>
       <c r="AG67" s="4" t="inlineStr">
@@ -11465,29 +11496,84 @@
           <t>Иран</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr"/>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Керманшах</t>
+        </is>
+      </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Iran University of Industries and Mines</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr"/>
+          <t>Kermanshah University of Technology</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>دانشگاه صنعتی کرمانشاه</t>
+        </is>
+      </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr"/>
-      <c r="H69" s="4" t="inlineStr"/>
-      <c r="I69" s="4" t="inlineStr"/>
-      <c r="J69" s="4" t="inlineStr"/>
-      <c r="K69" s="4" t="inlineStr"/>
+          <t>Технический / аэрокосмический</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Государственный (Минобрнауки Ирана, MSRT)</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>• Energy engineering (electrical, mechanical, chemical)
+• New technologies
+• Information technology &amp; computer engineering
+• Industrial engineering &amp; engineering management
+• Civil &amp; railway engineering</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>Kermanshah University of Technology, Imam Khomeini Highway, Kermanshah 6715685420, Iran</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>info@kut.ac.ir</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Sajjad Rasaei
+Руководитель Офиса президента, по связям с общественностью и международным делам
+Офис президента, по связям с общественностью и международным делам
+Обращение: Dear Dr. Rasaei,</t>
+        </is>
+      </c>
       <c r="L69" s="4" t="inlineStr"/>
-      <c r="M69" s="4" t="inlineStr"/>
-      <c r="N69" s="4" t="inlineStr"/>
-      <c r="O69" s="4" t="inlineStr"/>
-      <c r="P69" s="4" t="inlineStr"/>
-      <c r="Q69" s="4" t="inlineStr"/>
+      <c r="M69" s="4" t="inlineStr">
+        <is>
+          <t>info@kut.ac.ir</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>+98 83 3830 5002</t>
+        </is>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>https://kut.ac.ir (EN: https://kut.ac.ir/en)</t>
+        </is>
+      </c>
+      <c r="P69" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Hamed Rashidi</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="R69" s="4" t="inlineStr"/>
       <c r="S69" s="4" t="inlineStr"/>
       <c r="T69" s="4" t="inlineStr"/>
@@ -11508,19 +11594,35 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD69" s="4" t="inlineStr"/>
+      <c r="AD69" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE69" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF69" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт не найден: домены iuim.ac.ir / uim.ac.ir / iuim.ir не резолвятся, статьи в Wikipedia нет, квота веб-поиска исчерпана — ни один факт не подтверждён; форма собственности и город не установлены. Требуется ручная проверка (возможно, негосударственный вуз)
-• В санкционных списках ЕС/UK/США не найден; общие санкции против Ирана — нужна комплаенс-проверка</t>
-        </is>
-      </c>
-      <c r="AG69" s="4" t="inlineStr"/>
+          <t>• САНКЦИИ: В загруженных списках (US CSL/Entity List, OFAC SDN, EU consolidated, UK Sanctions List, версии на 10.2026) университет как организация НЕ найден; общий страновой санкционный режим в отношении Ирана сохраняется — требуется комплаенс-проверка до отправки приглашения
+• THE2027 — статус Reporter (без ранга), поэтому rank_the пуст
+• Президент Dr. Hamed Rashidi (доцент кафедры химической инженерии; назначен и.о. в марте 2025 г., на сайте 2026 г. — President)
+• Международные дела объединены с офисом президента и PR: «دفتر ریاست، روابط عمومی و امور بین الملل», руководитель — Dr. Sajjad Rasaei; отдельного e-mail международного отдела нет, используется info@kut.ac.ir
+• Profile_type «technical/aerospace» означает технический университет; аэрокосмических подразделений не выявлено
+• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0</t>
+        </is>
+      </c>
+      <c r="AG69" s="4" t="inlineStr">
+        <is>
+          <t>• Https://kut.ac.ir/en
+• Https://kut.ac.ir/en/university-president
+• Https://kut.ac.ir/contacts-2/
+• Https://kut.ac.ir/ (دفتر ریاست، روابط عمومی و امور بین الملل page)
+• Https://fa.wikipedia.org/wiki/دانشگاه_صنعتی_کرمانشاه</t>
+        </is>
+      </c>
       <c r="AH69" s="4" t="inlineStr">
         <is>
           <t>2026-10-04</t>
@@ -11539,22 +11641,22 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Керманшах</t>
+          <t>Хорремшехр</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Kermanshah University of Technology</t>
+          <t>Khorramshahr University of Marine Science and Technology</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه صنعتی کرمانشاه</t>
+          <t>دانشگاه علوم و فنون دریایی خرمشهر</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Технический / аэрокосмический</t>
+          <t>Морской / океанографический</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -11564,52 +11666,25 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>• Energy engineering (electrical, mechanical, chemical)
-• New technologies
-• Information technology &amp; computer engineering
-• Industrial engineering &amp; engineering management
-• Civil &amp; railway engineering</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>Kermanshah University of Technology, Imam Khomeini Highway, Kermanshah 6715685420, Iran</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>info@kut.ac.ir</t>
-        </is>
-      </c>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>Dr. Sajjad Rasaei
-Руководитель Офиса президента, по связям с общественностью и международным делам
-Офис президента, по связям с общественностью и международным делам
-Обращение: Dear Dr. Rasaei,</t>
-        </is>
-      </c>
+          <t>• Marine science
+• Marine biology
+• Fisheries
+• Marine engineering
+• Physical oceanography</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="4" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr"/>
       <c r="L70" s="4" t="inlineStr"/>
-      <c r="M70" s="4" t="inlineStr">
-        <is>
-          <t>info@kut.ac.ir</t>
-        </is>
-      </c>
-      <c r="N70" s="4" t="inlineStr">
-        <is>
-          <t>+98 83 3830 5002</t>
-        </is>
-      </c>
+      <c r="M70" s="4" t="inlineStr"/>
+      <c r="N70" s="4" t="inlineStr"/>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>https://kut.ac.ir (EN: https://kut.ac.ir/en)</t>
-        </is>
-      </c>
-      <c r="P70" s="4" t="inlineStr">
-        <is>
-          <t>Dr. Hamed Rashidi</t>
-        </is>
-      </c>
+          <t>https://kmsu.ac.ir</t>
+        </is>
+      </c>
+      <c r="P70" s="4" t="inlineStr"/>
       <c r="Q70" s="4" t="inlineStr">
         <is>
           <t>President</t>
@@ -11635,33 +11710,30 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD70" s="4" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="AD70" s="4" t="inlineStr"/>
       <c r="AE70" s="4" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>низкая</t>
         </is>
       </c>
       <c r="AF70" s="4" t="inlineStr">
         <is>
-          <t>• САНКЦИИ: В загруженных списках (US CSL/Entity List, OFAC SDN, EU consolidated, UK Sanctions List, версии на 10.2026) университет как организация НЕ найден; общий страновой санкционный режим в отношении Ирана сохраняется — требуется комплаенс-проверка до отправки приглашения
-• THE2027 — статус Reporter (без ранга), поэтому rank_the пуст
-• Президент Dr. Hamed Rashidi (доцент кафедры химической инженерии; назначен и.о. в марте 2025 г., на сайте 2026 г. — President)
-• Международные дела объединены с офисом президента и PR: «دفتر ریاست، روابط عمومی و امور بین الملل», руководитель — Dr. Sajjad Rasaei; отдельного e-mail международного отдела нет, используется info@kut.ac.ir
-• Profile_type «technical/aerospace» означает технический университет; аэрокосмических подразделений не выявлено
-• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0</t>
+          <t>• Сайт kmsu.ac.ir недоступен (таймаут / HTTP 503), статьи в Википедии нет — контакты, адрес и руководитель не подтверждены; лимит веб-поиска исчерпан
+• Основные направления указаны по названию/профилю (морской университет), официальной страницей не подтверждены
+• Космическая проверка (LIGHT) — только по nanosats.csv/Gunter's Space Page: спутников не найдено (лимит веб-поиска исчерпан, отдельный поиск не выполнялся)
+• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки
+• Перепроверка: Сайт kmsu.ac.ir (с www и без) недоступен (503 / сброс соединения) — данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG70" s="4" t="inlineStr">
         <is>
-          <t>• Https://kut.ac.ir/en
-• Https://kut.ac.ir/en/university-president
-• Https://kut.ac.ir/contacts-2/
-• Https://kut.ac.ir/ (دفتر ریاست، روابط عمومی و امور بین الملل page)
-• Https://fa.wikipedia.org/wiki/دانشگاه_صنعتی_کرمانشاه</t>
+          <t>• Https://kmsu.ac.ir (unreachable)
+• Https://www.timeshighereducation.com/world-university-rankings/latest/world-ranking
+• Https://sanctionslist.ofac.treas.gov (SDN)
+• Https://data.trade.gov/downloadable_consolidated_screening_list/v1/consolidated.csv (incl. BIS Entity List)
+• Https://webgate.ec.europa.eu/fsd/fsf (EU consolidated list)
+• Https://sanctionslist.fcdo.gov.uk/docs/UK-Sanctions-List.csv
+• Https://www.nanosats.eu (local export nanosats.csv)</t>
         </is>
       </c>
       <c r="AH70" s="4" t="inlineStr">
@@ -11682,22 +11754,22 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Хорремшехр</t>
+          <t>Малайер</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Khorramshahr University of Marine Science and Technology</t>
+          <t>Malayer University</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه علوم و فنون دریایی خرمشهر</t>
+          <t>دانشگاه ملایر</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Морской / океанографический</t>
+          <t>Классический</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -11707,28 +11779,56 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>• Marine science
-• Marine biology
-• Fisheries
-• Marine engineering
-• Physical oceanography</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="4" t="inlineStr"/>
-      <c r="K71" s="4" t="inlineStr"/>
+          <t>• Engineering
+• Civil engineering &amp; architecture
+• Basic sciences
+• Mathematics &amp; statistics
+• Agriculture
+• Natural resources &amp; environment</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>Malayer University, Km 4 Malayer–Arak Road, Malayer, Postal Code 65741-84621, Hamadan Province, Iran</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>pr@malayeru.ac.ir</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>ФИО не найдено
+Руководитель Бюро международных связей
+Канцелярия президента и служба связей с общественностью (دفتر ریاست و روابط عمومی)
+Обращение: Dear Director of International Relations,</t>
+        </is>
+      </c>
       <c r="L71" s="4" t="inlineStr"/>
-      <c r="M71" s="4" t="inlineStr"/>
-      <c r="N71" s="4" t="inlineStr"/>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>pr@malayeru.ac.ir</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>+98 81 3245 7300 (общий); +98 81 3245 7305 (офис руководителя), факс +98 81 3245 7306</t>
+        </is>
+      </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>https://kmsu.ac.ir</t>
-        </is>
-      </c>
-      <c r="P71" s="4" t="inlineStr"/>
+          <t>https://malayeru.ac.ir</t>
+        </is>
+      </c>
+      <c r="P71" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Mohammad Bashirgonbad (دکتر محمد بشیرگنبد)</t>
+        </is>
+      </c>
       <c r="Q71" s="4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Acting President (سرپرست دانشگاه)</t>
         </is>
       </c>
       <c r="R71" s="4" t="inlineStr"/>
@@ -11751,29 +11851,31 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD71" s="4" t="inlineStr"/>
+      <c r="AD71" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE71" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF71" s="4" t="inlineStr">
         <is>
-          <t>• Сайт kmsu.ac.ir недоступен (таймаут / HTTP 503), статьи в Википедии нет — контакты, адрес и руководитель не подтверждены; лимит веб-поиска исчерпан
-• Основные направления указаны по названию/профилю (морской университет), официальной страницей не подтверждены
-• Космическая проверка (LIGHT) — только по nanosats.csv/Gunter's Space Page: спутников не найдено (лимит веб-поиска исчерпан, отдельный поиск не выполнялся)
-• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки</t>
+          <t>• Руководитель исправлен: официальный сайт в новостях сентября–октября 2026 г. называет д-ра Мохаммада Баширгонбада «сرپرست» (и.о. руководителя) университета; ранее указанный д-р Хосров Сайванд (фа-Википедия) на сайте не упоминается
+• Email_general — адрес службы связей с общественностью (pr@malayeru.ac.ir, на сайте в виде pr[at]malayeru.ac.ir); у Бюро международных связей и иностранных студентов (اداره روابط بین الملل و دانشجویان غیرایرانی) e-mail не опубликован
+• Почтовый индекс на сайте записан «84621-65741» (RTL) — в нормальном порядке 65741-84621
+• Спутников не найдено (быстрая проверка)
+• Перепроверка: Сайт открыт через reader-сервис 04.10.2026: руководитель исправлен — и.о. президента (سرپرست) д-р Мохаммад Баширгонбад (новости сайта, мехр 1405 = сент.–окт. 2026); pr@malayeru.ac.ir, телефоны и адрес подтверждены на странице контактов (дата страницы 2019)</t>
         </is>
       </c>
       <c r="AG71" s="4" t="inlineStr">
         <is>
-          <t>• Https://kmsu.ac.ir (unreachable)
-• Https://www.timeshighereducation.com/world-university-rankings/latest/world-ranking
-• Https://sanctionslist.ofac.treas.gov (SDN)
-• Https://data.trade.gov/downloadable_consolidated_screening_list/v1/consolidated.csv (incl. BIS Entity List)
-• Https://webgate.ec.europa.eu/fsd/fsf (EU consolidated list)
-• Https://sanctionslist.fcdo.gov.uk/docs/UK-Sanctions-List.csv
-• Https://www.nanosats.eu (local export nanosats.csv)</t>
+          <t>• Https://malayeru.ac.ir/
+• Https://malayeru.ac.ir/en/
+• Https://malayeru.ac.ir/portal/home/?person/1430/33245/32806/
+• Https://fa.wikipedia.org/wiki/%D8%AF%D8%A7%D9%86%D8%B4%DA%AF%D8%A7%D9%87_%D9%85%D9%84%D8%A7%DB%8C%D8%B1</t>
         </is>
       </c>
       <c r="AH71" s="4" t="inlineStr">
@@ -11794,76 +11896,75 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Малайер</t>
+          <t>Абадан</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Malayer University</t>
+          <t>Petroleum University of Technology (PUT)</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه ملایر</t>
+          <t>دانشگاه صنعت نفت</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Классический</t>
+          <t>Технический / аэрокосмический</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>Государственный (Минобрнауки Ирана, MSRT)</t>
+          <t>Государственный (Министерство нефти Ирана)</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>• Engineering
-• Civil engineering &amp; architecture
-• Basic sciences
-• Mathematics &amp; statistics
-• Agriculture
-• Natural resources &amp; environment</t>
+          <t>• Petroleum engineering
+• Chemical &amp; gas engineering
+• Mechanical &amp; electrical/instrumentation engineering
+• Marine sciences (offshore oil &amp; gas)
+• Accounting &amp; finance</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>Malayer University, Km 4 Malayer–Arak Road, Malayer, Postal Code 65741-84621, Hamadan Province, Iran</t>
+          <t>Petroleum University of Technology, North Bovardeh, Abadan, Khuzestan, Iran (Postal Code 63187-14317)</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>pr@malayeru.ac.ir</t>
+          <t>info@put.ac.ir</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
           <t>ФИО не найдено
-Руководитель Бюро международных связей
-Канцелярия президента и служба связей с общественностью (دفتر ریاست و روابط عمومی)
-Обращение: Dear Director of International Relations,</t>
+Вице-президент по международным делам
+Общий ящик университета (info@put.ac.ir)
+Обращение: Dear Vice President for International Affairs,</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr"/>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>pr@malayeru.ac.ir</t>
+          <t>info@put.ac.ir</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>+98 81 3245 7300</t>
+          <t>+98 61 5315 3000</t>
         </is>
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>https://malayeru.ac.ir</t>
+          <t>https://put.ac.ir</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>Dr. Khosrow Sayvand</t>
+          <t>Dr. Mohammad Reza Khosravi-Nikou</t>
         </is>
       </c>
       <c r="Q72" s="4" t="inlineStr">
@@ -11872,7 +11973,11 @@
         </is>
       </c>
       <c r="R72" s="4" t="inlineStr"/>
-      <c r="S72" s="4" t="inlineStr"/>
+      <c r="S72" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter (unranked)</t>
+        </is>
+      </c>
       <c r="T72" s="4" t="inlineStr"/>
       <c r="U72" s="4" t="n">
         <v>0</v>
@@ -11898,154 +12003,10 @@
       </c>
       <c r="AE72" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF72" s="4" t="inlineStr">
-        <is>
-          <t>• Официальный портал устарел (новости 2019–2020): страница «президент» показывает д-ра Мохаммада Баширгонбада, а фа-Википедия и сводка МСРТ — д-ра Хосрова Сайванда. Указан Сайванд; ПЕРЕД рассылкой подтвердить
-• Email_general — адрес службы связей с общественностью (pr@malayeru.ac.ir); e-mail международного бюро (International Relations Bureau and Foreign Students Affairs) не опубликован
-• Почтовый индекс на сайте записан «84621-65741» (RTL), на англ. странице начинается с 6571… — сверить
-• Спутников не найдено (быстрая проверка)</t>
-        </is>
-      </c>
-      <c r="AG72" s="4" t="inlineStr">
-        <is>
-          <t>• Https://malayeru.ac.ir/
-• Https://malayeru.ac.ir/en/
-• Https://malayeru.ac.ir/portal/home/?person/1430/33245/32806/
-• Https://fa.wikipedia.org/wiki/%D8%AF%D8%A7%D9%86%D8%B4%DA%AF%D8%A7%D9%87_%D9%85%D9%84%D8%A7%DB%8C%D8%B1</t>
-        </is>
-      </c>
-      <c r="AH72" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI72" s="4" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Иран</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>Абадан</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>Petroleum University of Technology (PUT)</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>دانشگاه صنعت نفت</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Технический / аэрокосмический</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>Государственный (Министерство нефти Ирана)</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>• Petroleum engineering
-• Chemical &amp; gas engineering
-• Mechanical &amp; electrical/instrumentation engineering
-• Marine sciences (offshore oil &amp; gas)
-• Accounting &amp; finance</t>
-        </is>
-      </c>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>Petroleum University of Technology, North Bovardeh, Abadan, Khuzestan, Iran (Postal Code 63187-14317)</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>info@put.ac.ir</t>
-        </is>
-      </c>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>ФИО не найдено
-Вице-президент по международным делам
-Общий ящик университета (info@put.ac.ir)
-Обращение: Dear Vice President for International Affairs,</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="inlineStr"/>
-      <c r="M73" s="4" t="inlineStr">
-        <is>
-          <t>info@put.ac.ir</t>
-        </is>
-      </c>
-      <c r="N73" s="4" t="inlineStr">
-        <is>
-          <t>+98 61 5315 3000</t>
-        </is>
-      </c>
-      <c r="O73" s="4" t="inlineStr">
-        <is>
-          <t>https://put.ac.ir</t>
-        </is>
-      </c>
-      <c r="P73" s="4" t="inlineStr">
-        <is>
-          <t>Dr. Mohammad Reza Khosravi-Nikou</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="R73" s="4" t="inlineStr"/>
-      <c r="S73" s="4" t="inlineStr">
-        <is>
-          <t>THE2027: Reporter (unranked)</t>
-        </is>
-      </c>
-      <c r="T73" s="4" t="inlineStr"/>
-      <c r="U73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" s="4" t="inlineStr"/>
-      <c r="W73" s="4" t="inlineStr"/>
-      <c r="X73" s="4" t="inlineStr"/>
-      <c r="Y73" s="4" t="inlineStr"/>
-      <c r="Z73" s="4" t="inlineStr"/>
-      <c r="AA73" s="4" t="inlineStr"/>
-      <c r="AB73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC73" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD73" s="4" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="AE73" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AF73" s="4" t="inlineStr">
         <is>
           <t>• Подчиняется Министерству нефти Ирана (не MSRT); факультеты в Абадане, Ахвазе, Тегеране и Махмудабаде; центральный адрес — Абадан
 • Есть «Вице-президентство по международным делам и специализированному/прикладному обучению» (тел. +98 21 4424 9754, Тегеран), но e-mail и имя руководителя не найдены
@@ -12054,7 +12015,7 @@
 • Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки</t>
         </is>
       </c>
-      <c r="AG73" s="4" t="inlineStr">
+      <c r="AG72" s="4" t="inlineStr">
         <is>
           <t>• Https://put.ac.ir/
 • Https://put.ac.ir/fa-IR/put/5009
@@ -12069,48 +12030,48 @@
 • Https://www.nanosats.eu (local export nanosats.csv)</t>
         </is>
       </c>
-      <c r="AH73" s="4" t="inlineStr">
+      <c r="AH72" s="4" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="AI73" s="4" t="inlineStr"/>
+      <c r="AI72" s="4" t="inlineStr"/>
     </row>
-    <row r="74">
-      <c r="A74" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>Иран</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>Кум</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>Qom University of Technology</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>دانشگاه صنعتی قم</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>Технический / аэрокосмический</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="G73" s="4" t="inlineStr">
         <is>
           <t>Государственный (Минобрнауки Ирана, MSRT)</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
+      <c r="H73" s="4" t="inlineStr">
         <is>
           <t>• Electrical engineering
 • Computer engineering
@@ -12120,9 +12081,127 @@
 • Industrial engineering</t>
         </is>
       </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>Qom University of Technology, Shahid Sardar Khodakaram Blvd., Old Qom–Tehran Road, Qom, Postal Code 151937195, Iran</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr"/>
+      <c r="M73" s="4" t="inlineStr"/>
+      <c r="N73" s="4" t="inlineStr"/>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.qut.ac.ir</t>
+        </is>
+      </c>
+      <c r="P73" s="4" t="inlineStr"/>
+      <c r="Q73" s="4" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="R73" s="4" t="inlineStr"/>
+      <c r="S73" s="4" t="inlineStr">
+        <is>
+          <t>THE2027 Reporter (unranked)</t>
+        </is>
+      </c>
+      <c r="T73" s="4" t="inlineStr"/>
+      <c r="U73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="4" t="inlineStr"/>
+      <c r="W73" s="4" t="inlineStr"/>
+      <c r="X73" s="4" t="inlineStr"/>
+      <c r="Y73" s="4" t="inlineStr"/>
+      <c r="Z73" s="4" t="inlineStr"/>
+      <c r="AA73" s="4" t="inlineStr"/>
+      <c r="AB73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD73" s="4" t="inlineStr"/>
+      <c r="AE73" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+      <c r="AF73" s="4" t="inlineStr">
+        <is>
+          <t>• Официальный сайт qut.ac.ir недоступен из нашей сети — контакты не проверены
+• Fa-Википедия указывает президентом Джалала Резаи-Нура «с 24 тира 1397» (2018) — сведения могут быть устаревшими, поле оставлено пустым
+• THE2027: только статус Reporter. Адрес и индекс — по профилю THE (индекс 151937195 выглядит неполным — сверить)
+• Проверка на спутники не проведена (исчерпан лимит поиска)
+• Перепроверка: Сайт qut.ac.ir (и en.) недоступен из нашей сети (curl/WebFetch 503) 04.10.2026; данные не изменены</t>
+        </is>
+      </c>
+      <c r="AG73" s="4" t="inlineStr">
+        <is>
+          <t>• Https://en.wikipedia.org/wiki/Qom_University_of_Technology
+• Https://fa.wikipedia.org/wiki/%D8%AF%D8%A7%D9%86%D8%B4%DA%AF%D8%A7%D9%87_%D8%B5%D9%86%D8%B9%D8%AA%DB%8C_%D9%82%D9%85
+• Https://www.timeshighereducation.com/world-university-rankings/qom-university-technology</t>
+        </is>
+      </c>
+      <c r="AH73" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AI73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Иран</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Ахваз</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Shahid Chamran University of Ahvaz</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>دانشگاه شهید چمران اهواز</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Классический</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Государственный (Минобрнауки Ирана, MSRT)</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>• Agriculture
+• Engineering
+• Water &amp; environmental engineering
+• Basic sciences
+• Veterinary medicine
+• Humanities</t>
+        </is>
+      </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>Qom University of Technology, Shahid Sardar Khodakaram Blvd., Old Qom–Tehran Road, Qom, Postal Code 151937195, Iran</t>
+          <t>Shahid Chamran University of Ahvaz, Golestan Blvd., Ahvaz, Khuzestan Province, Iran</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr"/>
@@ -12132,21 +12211,21 @@
       <c r="N74" s="4" t="inlineStr"/>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>https://www.qut.ac.ir</t>
-        </is>
-      </c>
-      <c r="P74" s="4" t="inlineStr"/>
+          <t>https://scu.ac.ir</t>
+        </is>
+      </c>
+      <c r="P74" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Ali-Hossein Hosseinzadeh</t>
+        </is>
+      </c>
       <c r="Q74" s="4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Acting President</t>
         </is>
       </c>
       <c r="R74" s="4" t="inlineStr"/>
-      <c r="S74" s="4" t="inlineStr">
-        <is>
-          <t>THE2027 Reporter (unranked)</t>
-        </is>
-      </c>
+      <c r="S74" s="4" t="inlineStr"/>
       <c r="T74" s="4" t="inlineStr"/>
       <c r="U74" s="4" t="n">
         <v>0</v>
@@ -12173,17 +12252,18 @@
       </c>
       <c r="AF74" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт qut.ac.ir недоступен из нашей сети — контакты не проверены
-• Fa-Википедия указывает президентом Джалала Резаи-Нура «с 24 тира 1397» (2018) — сведения могут быть устаревшими, поле оставлено пустым
-• THE2027: только статус Reporter. Адрес и индекс — по профилю THE (индекс 151937195 выглядит неполным — сверить)
-• Проверка на спутники не проведена (исчерпан лимит поиска)</t>
+          <t>• Официальный сайт scu.ac.ir недоступен (антибот-заглушка) — контакты не проверены
+• Али-Хосейн Хосейнзаде — исполняющий обязанности президента (سرپرست) с 20 эсфанда 1403 (март 2025) по en/fa-Википедии со ссылкой на сайт вуза; мог быть утверждён или заменён — проверить
+• Во входных данных ранг THE2027 не указан; адрес — по профилю THE (Golestan Blvd, Ahvaz)
+• Проверка на спутники не проведена (исчерпан лимит поиска)
+• Перепроверка: 04.10.2026: scu.ac.ir недоступен (сброс соединения); поиск по-прежнему указывает А.-Х. Хосейнзаде как и.о. президента — данные не изменены</t>
         </is>
       </c>
       <c r="AG74" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.wikipedia.org/wiki/Qom_University_of_Technology
-• Https://fa.wikipedia.org/wiki/%D8%AF%D8%A7%D9%86%D8%B4%DA%AF%D8%A7%D9%87_%D8%B5%D9%86%D8%B9%D8%AA%DB%8C_%D9%82%D9%85
-• Https://www.timeshighereducation.com/world-university-rankings/qom-university-technology</t>
+          <t>• Https://en.wikipedia.org/wiki/Shahid_Chamran_University_of_Ahvaz
+• Https://fa.wikipedia.org/wiki/%D8%AF%D8%A7%D9%86%D8%B4%DA%AF%D8%A7%D9%87_%D8%B4%D9%87%DB%8C%D8%AF_%DA%86%D9%85%D8%B1%D8%A7%D9%86_%D8%A7%D9%87%D9%88%D8%A7%D8%B2
+• Https://www.timeshighereducation.com/world-university-rankings/shahid-chamran-university-ahvaz</t>
         </is>
       </c>
       <c r="AH74" s="4" t="inlineStr">
@@ -12204,62 +12284,86 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Ахваз</t>
+          <t>Тегеран</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Shahid Chamran University of Ahvaz</t>
+          <t>Shahid Rajaee Teacher Training University</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه شهید چمران اهواز</t>
+          <t>دانشگاه تربیت دبیر شهید رجایی</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Классический</t>
+          <t>Технический / аэрокосмический</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Государственный (Минобрнауки Ирана, MSRT)</t>
+          <t>Государственный (Министерство образования Ирана; MSRT-аккредитация)</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>• Agriculture
-• Engineering
-• Water &amp; environmental engineering
+          <t>• Mechanical
+• Electrical &amp; computer engineering
+• Civil engineering &amp; architecture
+• Materials engineering
 • Basic sciences
-• Veterinary medicine
-• Humanities</t>
+• Humanities &amp; teacher education
+• Art</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>Shahid Chamran University of Ahvaz, Golestan Blvd., Ahvaz, Khuzestan Province, Iran</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="inlineStr"/>
-      <c r="K75" s="4" t="inlineStr"/>
-      <c r="L75" s="4" t="inlineStr"/>
-      <c r="M75" s="4" t="inlineStr"/>
-      <c r="N75" s="4" t="inlineStr"/>
+          <t>Shahid Rajaee Teacher Training University, Shahid Shabanlou St., Lavizan, Tehran, P.O. Box 16785-163, Postal Code 1678815811, Iran</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>int.affairs@sru.ac.ir</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>ФИО не найдено
+Руководитель Офиса научного сотрудничества и международных дел
+Офис научного сотрудничества и международных дел
+Обращение: Dear Director of International Scientific Cooperation,</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>int.affairs@sru.ac.ir</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="inlineStr">
+        <is>
+          <t>sru@sru.ac.ir</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>+98 21 2297 0060</t>
+        </is>
+      </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>https://scu.ac.ir</t>
+          <t>https://www.sru.ac.ir</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Dr. Ali-Hossein Hosseinzadeh</t>
+          <t>Prof. Ali Pourkamali Anaraki</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
         <is>
-          <t>Acting President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="R75" s="4" t="inlineStr"/>
@@ -12282,25 +12386,30 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD75" s="4" t="inlineStr"/>
+      <c r="AD75" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE75" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF75" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт scu.ac.ir недоступен (антибот-заглушка) — контакты не проверены
-• Али-Хосейн Хосейнзаде — исполняющий обязанности президента (سرپرست) с 20 эсфанда 1403 (март 2025) по en/fa-Википедии со ссылкой на сайт вуза; мог быть утверждён или заменён — проверить
-• Во входных данных ранг THE2027 не указан; адрес — по профилю THE (Golestan Blvd, Ahvaz)
-• Проверка на спутники не проведена (исчерпан лимит поиска)</t>
+          <t>• Президент — проф. Али Пуркамали Анараки (механика, «استاد»), e-mail president@sru.ac.ir; назначается министром образования по согласованию с МСРТ
+• Международный офис (دفتر همکاری های علمی و امور بین الملل): тел. +98 21 2297 0029, факс +98 21 2297 0033; имя руководителя на открытых страницах не указано (поисковик называет д-ра Моджтабу Горбани — не подтверждено)
+• Англоязычный сайт использует также домен srttu.edu (sru@srttu.edu)
+• Спутников не найдено (быстрая проверка)</t>
         </is>
       </c>
       <c r="AG75" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.wikipedia.org/wiki/Shahid_Chamran_University_of_Ahvaz
-• Https://fa.wikipedia.org/wiki/%D8%AF%D8%A7%D9%86%D8%B4%DA%AF%D8%A7%D9%87_%D8%B4%D9%87%DB%8C%D8%AF_%DA%86%D9%85%D8%B1%D8%A7%D9%86_%D8%A7%D9%87%D9%88%D8%A7%D8%B2
-• Https://www.timeshighereducation.com/world-university-rankings/shahid-chamran-university-ahvaz</t>
+          <t>• Https://www.sru.ac.ir/
+• Https://www.sru.ac.ir/%d8%ad%d9%88%d8%b2%d9%87-%d8%b1%db%8c%d8%a7%d8%b3%d8%aa/%d8%b1%db%8c%d8%a7%d8%b3%d8%aa-%d8%af%d8%a7%d9%86%d8%b4%da%af%d8%a7%d9%87/
+• Https://www.sru.ac.ir/%D8%AD%D9%88%D8%B2%D9%87-%D8%B1%DB%8C%D8%A7%D8%B3%D8%AA/%D8%A7%D9%85%D9%88%D8%B1-%D8%A8%DB%8C%D9%86-%D8%A7%D9%84%D9%85%D9%84%D9%84/
+• Http://www.sru.ac.ir/en</t>
         </is>
       </c>
       <c r="AH75" s="4" t="inlineStr">
@@ -12321,17 +12430,17 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Тегеран</t>
+          <t>Шахруд</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Shahid Rajaee Teacher Training University</t>
+          <t>Shahrood University of Technology</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه تربیت دبیر شهید رجایی</t>
+          <t>دانشگاه صنعتی شاهرود</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -12341,61 +12450,56 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Государственный (Министерство образования Ирана; MSRT-аккредитация)</t>
+          <t>Государственный (Минобрнауки Ирана, MSRT)</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>• Mechanical
-• Electrical &amp; computer engineering
-• Civil engineering &amp; architecture
-• Materials engineering
-• Basic sciences
-• Humanities &amp; teacher education
-• Art</t>
+          <t>• Mining Engineering
+• Mechanical Engineering
+• Electrical and Robotics Engineering
+• Civil Engineering
+• Chemical Engineering
+• Basic Sciences</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>Shahid Rajaee Teacher Training University, Shahid Shabanlou St., Lavizan, Tehran, P.O. Box 16785-163, Postal Code 1678815811, Iran</t>
+          <t>Daneshgah Blvd., P.O. Box 3619995161, Shahrood, Semnan Province, Iran</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>int.affairs@sru.ac.ir</t>
+          <t>International@shahroodut.ac.ir</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
           <t>ФИО не найдено
-Руководитель Офиса научного сотрудничества и международных дел
-Офис научного сотрудничества и международных дел
+Директор по научному и международному сотрудничеству
+Управление научного и международного сотрудничества
 Обращение: Dear Director of International Scientific Cooperation,</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>int.affairs@sru.ac.ir</t>
-        </is>
-      </c>
-      <c r="M76" s="4" t="inlineStr">
-        <is>
-          <t>sru@sru.ac.ir</t>
-        </is>
-      </c>
+          <t>International@shahroodut.ac.ir</t>
+        </is>
+      </c>
+      <c r="M76" s="4" t="inlineStr"/>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>+98 21 2297 0060</t>
+          <t>+98 23 3239 2204</t>
         </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>https://www.sru.ac.ir</t>
+          <t>https://www.shahroodut.ac.ir/en</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>Prof. Ali Pourkamali Anaraki</t>
+          <t>Dr. Morteza Izadifard</t>
         </is>
       </c>
       <c r="Q76" s="4" t="inlineStr">
@@ -12435,18 +12539,24 @@
       </c>
       <c r="AF76" s="4" t="inlineStr">
         <is>
-          <t>• Президент — проф. Али Пуркамали Анараки (механика, «استاد»), e-mail president@sru.ac.ir; назначается министром образования по согласованию с МСРТ
-• Международный офис (دفتر همکاری های علمی و امور بین الملل): тел. +98 21 2297 0029, факс +98 21 2297 0033; имя руководителя на открытых страницах не указано (поисковик называет д-ра Моджтабу Горбани — не подтверждено)
-• Англоязычный сайт использует также домен srttu.edu (sru@srttu.edu)
-• Спутников не найдено (быстрая проверка)</t>
+          <t>• Президент: д-р Мортеза Изадифард — переназначен министром науки на 4 года (Mehr «رئیس دانشگاه صنعتی شاهرود ابقا شد», SNN); один сниппет называл М. М. Фатеха — устаревшие данные
+• International@shahroodut.ac.ir — Scientific and International Affairs Office, тел. +98 23 3239 4931; имя директора не подтверждено
+• Вуз внесён в базу Iran Watch (Висконсинский проект, не санкционный список); упоминается в отчёте Iran Watch о БПЛА-исследованиях. Рядом находится космодром Шахруд (КСИР) — к университету не относится, но повышает репутационный риск
+• Быстрая проверка спутников: не найдено
+• Иран под всеобъемлющими санкциями США (ITSR/OFAC) и ограничительными мерами ЕС/Великобритании; перед контактом нужна юридическая/комплаенс-проверка
+• Санкционная проверка (кэш CSL США/SDN, ЕС, UK от 04.10.2026): университет не найден; restricted_list пуст
+• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой</t>
         </is>
       </c>
       <c r="AG76" s="4" t="inlineStr">
         <is>
-          <t>• Https://www.sru.ac.ir/
-• Https://www.sru.ac.ir/%d8%ad%d9%88%d8%b2%d9%87-%d8%b1%db%8c%d8%a7%d8%b3%d8%aa/%d8%b1%db%8c%d8%a7%d8%b3%d8%aa-%d8%af%d8%a7%d9%86%d8%b4%da%af%d8%a7%d9%87/
-• Https://www.sru.ac.ir/%D8%AD%D9%88%D8%B2%D9%87-%D8%B1%DB%8C%D8%A7%D8%B3%D8%AA/%D8%A7%D9%85%D9%88%D8%B1-%D8%A8%DB%8C%D9%86-%D8%A7%D9%84%D9%85%D9%84%D9%84/
-• Http://www.sru.ac.ir/en</t>
+          <t>• Https://en.wikipedia.org/wiki/Shahrood_University_of_Technology
+• Https://fa.wikipedia.org/wiki/دانشگاه_صنعتی_شاهرود
+• Https://www.mehrnews.com/news/6665614/
+• Https://snn.ir/fa/news/1335070/
+• Https://shahroodut.ac.ir/en/sec/index.php?id=44
+• Http://international.shahroodut.ac.ir/post/36/Contact-Us
+• Https://www.iranwatch.org/iranian-entities/shahrood-university-technology-sut</t>
         </is>
       </c>
       <c r="AH76" s="4" t="inlineStr">
@@ -12467,17 +12577,17 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Шахруд</t>
+          <t>Тафреш</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Shahrood University of Technology</t>
+          <t>Tafresh University</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه صنعتی شاهرود</t>
+          <t>دانشگاه تفرش</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -12492,51 +12602,23 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>• Mining Engineering
-• Mechanical Engineering
-• Electrical and Robotics Engineering
-• Civil Engineering
-• Chemical Engineering
-• Basic Sciences</t>
-        </is>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t>Daneshgah Blvd., P.O. Box 3619995161, Shahrood, Semnan Province, Iran</t>
-        </is>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>International@shahroodut.ac.ir</t>
-        </is>
-      </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>ФИО не найдено
-Директор по научному и международному сотрудничеству
-Управление научного и международного сотрудничества
-Обращение: Dear Director of International Scientific Cooperation,</t>
-        </is>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>International@shahroodut.ac.ir</t>
-        </is>
-      </c>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr"/>
+      <c r="J77" s="4" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr"/>
+      <c r="L77" s="4" t="inlineStr"/>
       <c r="M77" s="4" t="inlineStr"/>
-      <c r="N77" s="4" t="inlineStr">
-        <is>
-          <t>+98 23 3239 2204</t>
-        </is>
-      </c>
+      <c r="N77" s="4" t="inlineStr"/>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>https://www.shahroodut.ac.ir/en</t>
+          <t>https://tafreshu.ac.ir</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>Dr. Morteza Izadifard</t>
+          <t>Dr. Soheil Vasheghani Farahani (دکتر سهیل واشقانی فراهانی)</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
@@ -12564,36 +12646,32 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD77" s="4" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="AD77" s="4" t="inlineStr"/>
       <c r="AE77" s="4" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>низкая</t>
         </is>
       </c>
       <c r="AF77" s="4" t="inlineStr">
         <is>
-          <t>• Президент: д-р Мортеза Изадифард — переназначен министром науки на 4 года (Mehr «رئیس دانشگاه صنعتی شاهرود ابقا شد», SNN); один сниппет называл М. М. Фатеха — устаревшие данные
-• International@shahroodut.ac.ir — Scientific and International Affairs Office, тел. +98 23 3239 4931; имя директора не подтверждено
-• Вуз внесён в базу Iran Watch (Висконсинский проект, не санкционный список); упоминается в отчёте Iran Watch о БПЛА-исследованиях. Рядом находится космодром Шахруд (КСИР) — к университету не относится, но повышает репутационный риск
-• Быстрая проверка спутников: не найдено
-• Иран под всеобъемлющими санкциями США (ITSR/OFAC) и ограничительными мерами ЕС/Великобритании; перед контактом нужна юридическая/комплаенс-проверка
-• Санкционная проверка (кэш CSL США/SDN, ЕС, UK от 04.10.2026): университет не найден; restricted_list пуст
-• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой</t>
+          <t>• Ранее «Tafresh University of Technology» (دانشگاه صنعتی تفرش); город Тафреш, провинция Меркези
+• Космическая проверка (LIGHT) — только по nanosats.csv/Gunter's Space Page: спутников не найдено (лимит веб-поиска исчерпан, отдельный поиск не выполнялся)
+• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки
+• Сайт tafreshu.ac.ir недоступен (04.10.2026). Глава вуза д-р Сохейль Вашегани Фарахани назван «رئیس دانشگاه» в официальном Telegram-канале @tafreshu (ноябрь 2024); в постах 2025–2026 имя не встречается — актуальность не подтверждена. Указанный в Википедии д-р Махмудреза Шахверди, по-видимому, устарел
+• Контактов (e-mail/телефон/адрес) по-прежнему нет
+• Перепроверка: Через официальный Telegram-канал найден глава вуза (д-р Вашегани Фарахани, данные 11.2024, требуют проверки); сайт недоступен, контакты не найдены</t>
         </is>
       </c>
       <c r="AG77" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.wikipedia.org/wiki/Shahrood_University_of_Technology
-• Https://fa.wikipedia.org/wiki/دانشگاه_صنعتی_شاهرود
-• Https://www.mehrnews.com/news/6665614/
-• Https://snn.ir/fa/news/1335070/
-• Https://shahroodut.ac.ir/en/sec/index.php?id=44
-• Http://international.shahroodut.ac.ir/post/36/Contact-Us
-• Https://www.iranwatch.org/iranian-entities/shahrood-university-technology-sut</t>
+          <t>• Https://en.wikipedia.org/wiki/Tafresh_University
+• Https://fa.wikipedia.org/wiki/دانشگاه_تفرش
+• Https://www.timeshighereducation.com/world-university-rankings/latest/world-ranking
+• Https://sanctionslist.ofac.treas.gov (SDN)
+• Https://data.trade.gov/downloadable_consolidated_screening_list/v1/consolidated.csv (incl. BIS Entity List)
+• Https://webgate.ec.europa.eu/fsd/fsf (EU consolidated list)
+• Https://sanctionslist.fcdo.gov.uk/docs/UK-Sanctions-List.csv
+• Https://www.nanosats.eu (local export nanosats.csv)</t>
         </is>
       </c>
       <c r="AH77" s="4" t="inlineStr">
@@ -12614,17 +12692,17 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Тафреш</t>
+          <t>Бонаб</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Tafresh University</t>
+          <t>University of Bonab</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه تفرش</t>
+          <t>دانشگاه بناب</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -12639,21 +12717,57 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr"/>
-      <c r="J78" s="4" t="inlineStr"/>
-      <c r="K78" s="4" t="inlineStr"/>
-      <c r="L78" s="4" t="inlineStr"/>
-      <c r="M78" s="4" t="inlineStr"/>
-      <c r="N78" s="4" t="inlineStr"/>
+          <t>• Electrical Engineering
+• Mechanical Engineering
+• Civil Engineering
+• Materials and Polymer Engineering
+• Basic Sciences
+• Agriculture</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Velayat Highway, P.O. Box 5551761167, Bonab, East Azerbaijan, Iran</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>international@ubonab.ac.ir</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>ФИО не найдено
+Директор по международным делам
+Управление международных дел
+Обращение: Dear Director of International Affairs,</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>international@ubonab.ac.ir</t>
+        </is>
+      </c>
+      <c r="M78" s="4" t="inlineStr">
+        <is>
+          <t>info@ubonab.ac.ir</t>
+        </is>
+      </c>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>+98 41 3774 5000</t>
+        </is>
+      </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>https://tafreshu.ac.ir</t>
-        </is>
-      </c>
-      <c r="P78" s="4" t="inlineStr"/>
+          <t>https://en.ubonab.ac.ir</t>
+        </is>
+      </c>
+      <c r="P78" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Behzad Binesh</t>
+        </is>
+      </c>
       <c r="Q78" s="4" t="inlineStr">
         <is>
           <t>President</t>
@@ -12679,30 +12793,35 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD78" s="4" t="inlineStr"/>
+      <c r="AD78" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE78" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF78" s="4" t="inlineStr">
         <is>
-          <t>• Сайт tafreshu.ac.ir (и en.tafreshu.ac.ir) недоступен (таймаут / HTTP 503) — контакты и руководитель не подтверждены. В Википедии указан д-р Махмудреза Шахверди (ссылка мёртвая, вероятно устарело)
-• Ранее «Tafresh University of Technology» (دانشگاه صنعتی تفرش); город Тафреш, провинция Меркези
-• Космическая проверка (LIGHT) — только по nanosats.csv/Gunter's Space Page: спутников не найдено (лимит веб-поиска исчерпан, отдельный поиск не выполнялся)
-• Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки</t>
+          <t>• THE2027: статус Reporter (без ранга) — rank_the оставлен пустым
+• Президент: д-р Бехзад Биниш (доцент) — с 28 мехра 1404 (окт. 2025) по fa Wikipedia, утверждён ВСКР (YJC: «تایید ۱۹ رئیس دانشگاه...»); en Wikipedia указывает предыдущего (К. Аббасиан)
+• International@ubonab.ac.ir — International Affairs (по сниппету официальной страницы); имя руководителя не подтверждено
+• Быстрая проверка спутников: не найдено
+• Иран под всеобъемлющими санкциями США (ITSR/OFAC) и ограничительными мерами ЕС/Великобритании; перед контактом нужна юридическая/комплаенс-проверка
+• Санкционная проверка (кэш CSL США/SDN, ЕС, UK от 04.10.2026): университет не найден; restricted_list пуст
+• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой</t>
         </is>
       </c>
       <c r="AG78" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.wikipedia.org/wiki/Tafresh_University
-• Https://fa.wikipedia.org/wiki/دانشگاه_تفرش
-• Https://www.timeshighereducation.com/world-university-rankings/latest/world-ranking
-• Https://sanctionslist.ofac.treas.gov (SDN)
-• Https://data.trade.gov/downloadable_consolidated_screening_list/v1/consolidated.csv (incl. BIS Entity List)
-• Https://webgate.ec.europa.eu/fsd/fsf (EU consolidated list)
-• Https://sanctionslist.fcdo.gov.uk/docs/UK-Sanctions-List.csv
-• Https://www.nanosats.eu (local export nanosats.csv)</t>
+          <t>• Https://en.wikipedia.org/wiki/University_of_Bonab
+• Https://fa.wikipedia.org/wiki/دانشگاه_بناب
+• Https://en.ubonab.ac.ir/Page/80/International-Affairs.html
+• Https://en.ubonab.ac.ir/
+• Https://www.yjc.ir/fa/news/9016043/
+• Https://pr.ubonab.ac.ir/News/2083/Welcome-Message.html</t>
         </is>
       </c>
       <c r="AH78" s="4" t="inlineStr">
@@ -12723,22 +12842,22 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Бонаб</t>
+          <t>Кум</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>University of Bonab</t>
+          <t>University of Hazrate Masoumeh</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه بناب</t>
+          <t>دانشگاه حضرت معصومه (س)</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Технический / аэрокосмический</t>
+          <t>Классический</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -12748,60 +12867,55 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>• Electrical Engineering
-• Mechanical Engineering
-• Civil Engineering
-• Materials and Polymer Engineering
+          <t>• Humanities
+• Engineering
 • Basic Sciences
-• Agriculture</t>
+• Arts
+• Social Sciences</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>Velayat Highway, P.O. Box 5551761167, Bonab, East Azerbaijan, Iran</t>
+          <t>University of Hazrate Masoumeh, Al-Ghadir Blvd., opposite Yadegar-e Emam Stadium, Qom 3736175515 (P.O. Box 37115-145), Iran</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>international@ubonab.ac.ir</t>
+          <t>info@hmu.ac.ir</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
           <t>ФИО не найдено
-Директор по международным делам
-Управление международных дел
-Обращение: Dear Director of International Affairs,</t>
-        </is>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>international@ubonab.ac.ir</t>
-        </is>
-      </c>
+Директор по международному научному сотрудничеству
+Общий ящик университета (канцелярия)
+Обращение: Dear Director of International Scientific Cooperation,</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr"/>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>info@ubonab.ac.ir</t>
+          <t>info@hmu.ac.ir</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>+98 41 3774 5000</t>
+          <t>+98 25 32012</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>https://en.ubonab.ac.ir</t>
+          <t>https://hmu.ac.ir</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>Dr. Behzad Binesh</t>
+          <t>Dr. Seyedeh Fatemeh Faghihi</t>
         </is>
       </c>
       <c r="Q79" s="4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Acting President</t>
         </is>
       </c>
       <c r="R79" s="4" t="inlineStr"/>
@@ -12826,33 +12940,30 @@
       </c>
       <c r="AD79" s="4" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="AE79" s="4" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>низкая</t>
         </is>
       </c>
       <c r="AF79" s="4" t="inlineStr">
         <is>
-          <t>• THE2027: статус Reporter (без ранга) — rank_the оставлен пустым
-• Президент: д-р Бехзад Биниш (доцент) — с 28 мехра 1404 (окт. 2025) по fa Wikipedia, утверждён ВСКР (YJC: «تایید ۱۹ رئیس دانشگاه...»); en Wikipedia указывает предыдущего (К. Аббасиан)
-• International@ubonab.ac.ir — International Affairs (по сниппету официальной страницы); имя руководителя не подтверждено
-• Быстрая проверка спутников: не найдено
-• Иран под всеобъемлющими санкциями США (ITSR/OFAC) и ограничительными мерами ЕС/Великобритании; перед контактом нужна юридическая/комплаенс-проверка
-• Санкционная проверка (кэш CSL США/SDN, ЕС, UK от 04.10.2026): университет не найден; restricted_list пуст
-• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой</t>
+          <t>• THE2027: Reporter (не ранжирован)
+• Руководитель: на персидской главной странице (новости 2026) — д-р Сейеде Фатеме Факихи, «сарпараст» (и.о. президента); английская страница President устарела (Maryam Bordbar)
+• Телефон опубликован в сокращённом виде «025-32012» (короткий номер); факс +98 25 3320 9050. Отдельного международного ящика не найдено — использовать info@hmu.ac.ir
+• Женский университет (только для студенток)
+• Космических проектов не выявлено (проверка только по nanosats.csv — квота веб-поиска исчерпана)
+• В санкционных списках ЕС/UK/США не найден; общие санкции против Ирана — нужна комплаенс-проверка
+• Перепроверка: Сайт hmu.ac.ir (включая en.) по-прежнему недоступен 04.10.2026; данные не изменены</t>
         </is>
       </c>
       <c r="AG79" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.wikipedia.org/wiki/University_of_Bonab
-• Https://fa.wikipedia.org/wiki/دانشگاه_بناب
-• Https://en.ubonab.ac.ir/Page/80/International-Affairs.html
-• Https://en.ubonab.ac.ir/
-• Https://www.yjc.ir/fa/news/9016043/
-• Https://pr.ubonab.ac.ir/News/2083/Welcome-Message.html</t>
+          <t>• Https://hmu.ac.ir
+• Https://hmu.ac.ir/Category/Content/article/en/17934/2259
+• Nanosats.csv</t>
         </is>
       </c>
       <c r="AH79" s="4" t="inlineStr">
@@ -12873,17 +12984,17 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Кум</t>
+          <t>Джирофт</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>University of Hazrate Masoumeh</t>
+          <t>University of Jiroft</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه حضرت معصومه (س)</t>
+          <t>دانشگاه جیرفت</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -12898,55 +13009,59 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>• Humanities
+          <t>• Agriculture &amp; Natural Resources
 • Engineering
 • Basic Sciences
-• Arts
-• Social Sciences</t>
+• Humanities
+• Veterinary/Animal Sciences</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>University of Hazrate Masoumeh, Al-Ghadir Blvd., opposite Yadegar-e Emam Stadium, Qom 3736175515 (P.O. Box 37115-145), Iran</t>
+          <t>University of Jiroft, Km 8 Persian Gulf Highway, Jiroft 7867155311, Kerman Province, Iran</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>info@hmu.ac.ir</t>
+          <t>m.moghbeli@ujiroft.ac.ir</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
-Директор по международному научному сотрудничеству
-Общий ящик университета (канцелярия)
-Обращение: Dear Director of International Scientific Cooperation,</t>
-        </is>
-      </c>
-      <c r="L80" s="4" t="inlineStr"/>
+          <t>Dr. Moslem Moghbeli Damaneh
+Руководитель канцелярии президента, PR и международных дел
+Управление канцелярии президента, связей с общественностью и международных дел
+Обращение: Dear Dr. Moghbeli Damaneh,</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>m.moghbeli@ujiroft.ac.ir</t>
+        </is>
+      </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>info@hmu.ac.ir</t>
+          <t>President@ujiroft.ac.ir</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>+98 25 32012</t>
+          <t>+98 34 4123 3000</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>https://hmu.ac.ir</t>
+          <t>https://ujiroft.ac.ir</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>Dr. Seyedeh Fatemeh Faghihi</t>
+          <t>Dr. Omid Ali Esmaeilipour</t>
         </is>
       </c>
       <c r="Q80" s="4" t="inlineStr">
         <is>
-          <t>Acting President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="R80" s="4" t="inlineStr"/>
@@ -12976,23 +13091,23 @@
       </c>
       <c r="AE80" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF80" s="4" t="inlineStr">
         <is>
-          <t>• THE2027: Reporter (не ранжирован)
-• Руководитель: на персидской главной странице (новости 2026) — д-р Сейеде Фатеме Факихи, «сарпараст» (и.о. президента); английская страница President устарела (Maryam Bordbar)
-• Телефон опубликован в сокращённом виде «025-32012» (короткий номер); факс +98 25 3320 9050. Отдельного международного ящика не найдено — использовать info@hmu.ac.ir
-• Женский университет (только для студенток)
+          <t>• Президент д-р Омидали Эсмаилипур (личный e-mail omid.esmaeilipour@ujiroft.ac.ir) — по странице «Президент» сайта; дата обновления не указана
+• Международные дела объединены с канцелярией президента и PR: руководитель д-р Мослем Могбели Даманэ; email_international — его личный адрес (отдельного ящика нет). Общий info@ujiroft.ac.ir указан на англ. сайте
 • Космических проектов не выявлено (проверка только по nanosats.csv — квота веб-поиска исчерпана)
 • В санкционных списках ЕС/UK/США не найден; общие санкции против Ирана — нужна комплаенс-проверка</t>
         </is>
       </c>
       <c r="AG80" s="4" t="inlineStr">
         <is>
-          <t>• Https://hmu.ac.ir
-• Https://hmu.ac.ir/Category/Content/article/en/17934/2259
+          <t>• Https://ujiroft.ac.ir/fa
+• Https://ujiroft.ac.ir/fa/page/215/ریاست
+• Https://ujiroft.ac.ir/fa/page/218/حوزه-ریاست-روابط-عمومی-و-امور-بین-الملل
+• Https://ujiroft.ac.ir/en
 • Nanosats.csv</t>
         </is>
       </c>
@@ -13014,79 +13129,75 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Джирофт</t>
+          <t>Тегеран</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>University of Jiroft</t>
+          <t>University of Science and Culture</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه جیرفت</t>
+          <t>دانشگاه علم و فرهنگ</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Классический</t>
+          <t>Другое</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Государственный (Минобрнауки Ирана, MSRT)</t>
+          <t>Частный (негосударственный некоммерческий, учреждён ACECR / Джахад-е Данешгахи)</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>• Agriculture &amp; Natural Resources
-• Engineering
-• Basic Sciences
-• Humanities
-• Veterinary/Animal Sciences</t>
+          <t>• Engineering (computer, industrial, electrical, textile)
+• Art &amp; architecture
+• Humanities &amp; social sciences
+• Management
+• Biotechnology &amp; life sciences (Royan Institute)</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>University of Jiroft, Km 8 Persian Gulf Highway, Jiroft 7867155311, Kerman Province, Iran</t>
+          <t>University of Science and Culture, Homa St., Bahar St., Shahid Qamoshi Ave., Ashrafi Esfahani Blvd., Tehran, Iran</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>m.moghbeli@ujiroft.ac.ir</t>
+          <t>info@usc.ac.ir</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>Dr. Moslem Moghbeli Damaneh
-Руководитель канцелярии президента, PR и международных дел
-Управление канцелярии президента, связей с общественностью и международных дел
-Обращение: Dear Dr. Moghbeli Damaneh,</t>
-        </is>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>m.moghbeli@ujiroft.ac.ir</t>
-        </is>
-      </c>
+          <t>Dr. Ali Saadollah
+Генеральный директор по международному сотрудничеству
+Общий ящик университета; адресат — Генеральный директорат международного сотрудничества
+Обращение: Dear Dr. Saadollah,</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr"/>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>President@ujiroft.ac.ir</t>
+          <t>info@usc.ac.ir</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>+98 34 4123 3000</t>
+          <t>+98 21 4425 0414</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>https://ujiroft.ac.ir</t>
+          <t>https://usc.ac.ir (EN: https://en.usc.ac.ir)</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>Dr. Omid Ali Esmaeilipour</t>
+          <t>Dr. Mohammad Imani Khoshkhoo</t>
         </is>
       </c>
       <c r="Q81" s="4" t="inlineStr">
@@ -13126,19 +13237,19 @@
       </c>
       <c r="AF81" s="4" t="inlineStr">
         <is>
-          <t>• Президент д-р Омидали Эсмаилипур (личный e-mail omid.esmaeilipour@ujiroft.ac.ir) — по странице «Президент» сайта; дата обновления не указана
-• Международные дела объединены с канцелярией президента и PR: руководитель д-р Мослем Могбели Даманэ; email_international — его личный адрес (отдельного ящика нет). Общий info@ujiroft.ac.ir указан на англ. сайте
-• Космических проектов не выявлено (проверка только по nanosats.csv — квота веб-поиска исчерпана)
-• В санкционных списках ЕС/UK/США не найден; общие санкции против Ирана — нужна комплаенс-проверка</t>
+          <t>• САНКЦИИ: В загруженных списках (US CSL/Entity List, OFAC SDN, EU consolidated, UK Sanctions List, версии на 10.2026) университет как организация НЕ найден; общий страновой санкционный режим в отношении Ирана сохраняется — требуется комплаенс-проверка до отправки приглашения
+• THE2027 — статус Reporter (без ранга), rank_the пуст
+• Негосударственный некоммерческий университет, учреждённый Академическим центром образования, культуры и исследований (ACECR); научные учёные звания президента и директора не указаны — используется «Dr.»
+• Отдельный e-mail международного офиса не найден; Генеральный директорат международного сотрудничества — директор Ali Saadollah (вн. тел. 618 по справочнику сайта). Письмо на info@usc.ac.ir с просьбой переадресовать
+• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0</t>
         </is>
       </c>
       <c r="AG81" s="4" t="inlineStr">
         <is>
-          <t>• Https://ujiroft.ac.ir/fa
-• Https://ujiroft.ac.ir/fa/page/215/ریاست
-• Https://ujiroft.ac.ir/fa/page/218/حوزه-ریاست-روابط-عمومی-و-امور-بین-الملل
-• Https://ujiroft.ac.ir/en
-• Nanosats.csv</t>
+          <t>• Https://en.usc.ac.ir/
+• Https://en.usc.ac.ir/contact-us/
+• Https://international.usc.ac.ir/en/
+• Https://en.wikipedia.org/wiki/University_of_Science_and_Culture</t>
         </is>
       </c>
       <c r="AH81" s="4" t="inlineStr">
@@ -13159,80 +13270,64 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Тегеран</t>
+          <t>Бехшехр</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>University of Science and Culture</t>
+          <t>University of Science and Technology of Mazandaran</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه علم و فرهنگ</t>
+          <t>دانشگاه علم و فناوری مازندران</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Другое</t>
+          <t>Технический / аэрокосмический</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Частный (негосударственный некоммерческий, учреждён ACECR / Джахад-е Данешгахи)</t>
+          <t>Государственный (Минобрнауки Ирана, MSRT)</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>• Engineering (computer, industrial, electrical, textile)
-• Art &amp; architecture
-• Humanities &amp; social sciences
-• Management
-• Biotechnology &amp; life sciences (Royan Institute)</t>
+          <t>• Mathematics
+• Electrical and Computer Engineering
+• Chemical Engineering
+• Industrial Engineering</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>University of Science and Culture, Homa St., Bahar St., Shahid Qamoshi Ave., Ashrafi Esfahani Blvd., Tehran, Iran</t>
-        </is>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>info@usc.ac.ir</t>
-        </is>
-      </c>
-      <c r="K82" s="4" t="inlineStr">
-        <is>
-          <t>Dr. Ali Saadollah
-Генеральный директор по международному сотрудничеству
-Общий ящик университета; адресат — Генеральный директорат международного сотрудничества
-Обращение: Dear Dr. Saadollah,</t>
-        </is>
-      </c>
+          <t>University Blvd., Sea Road, P.O. Box 48518-78195, Behshahr, Mazandaran, Iran</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr"/>
       <c r="L82" s="4" t="inlineStr"/>
-      <c r="M82" s="4" t="inlineStr">
-        <is>
-          <t>info@usc.ac.ir</t>
-        </is>
-      </c>
+      <c r="M82" s="4" t="inlineStr"/>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>+98 21 4425 0414</t>
+          <t>+98 11 3455 2008</t>
         </is>
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>https://usc.ac.ir (EN: https://en.usc.ac.ir)</t>
+          <t>https://en.mazust.ac.ir</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>Dr. Mohammad Imani Khoshkhoo</t>
+          <t>Dr. Ali Tahmasbi</t>
         </is>
       </c>
       <c r="Q82" s="4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Acting President</t>
         </is>
       </c>
       <c r="R82" s="4" t="inlineStr"/>
@@ -13255,31 +13350,30 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD82" s="4" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="AD82" s="4" t="inlineStr"/>
       <c r="AE82" s="4" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>низкая</t>
         </is>
       </c>
       <c r="AF82" s="4" t="inlineStr">
         <is>
-          <t>• САНКЦИИ: В загруженных списках (US CSL/Entity List, OFAC SDN, EU consolidated, UK Sanctions List, версии на 10.2026) университет как организация НЕ найден; общий страновой санкционный режим в отношении Ирана сохраняется — требуется комплаенс-проверка до отправки приглашения
-• THE2027 — статус Reporter (без ранга), rank_the пуст
-• Негосударственный некоммерческий университет, учреждённый Академическим центром образования, культуры и исследований (ACECR); научные учёные звания президента и директора не указаны — используется «Dr.»
-• Отдельный e-mail международного офиса не найден; Генеральный директорат международного сотрудничества — директор Ali Saadollah (вн. тел. 618 по справочнику сайта). Письмо на info@usc.ac.ir с просьбой переадресовать
-• Быстрая проверка спутников: web search в сессии исчерпан; в nanosats.csv (nation=Iran) и списке спутников ISA в Википедии университет не упоминается — 0</t>
+          <t>• Руководитель: д-р Али Тахмасби (прикл. математика) — назначен и.о. президента (Mehr «سرپرست دانشگاه علم و فناوری مازندران منصوب شد», ок. 2026) вместо А. Раббани; статус и.о
+• Не путать с Mazandaran University of Science and Technology (Баболь, ustmb.ac.ir) и University of Mazandaran (umz.ac.ir)
+• E-mail не найден; телефон из сниппета (+98 11 3455 2008) — перепроверить
+• Быстрая проверка спутников: не найдено
+• Иран под всеобъемлющими санкциями США (ITSR/OFAC) и ограничительными мерами ЕС/Великобритании; перед контактом нужна юридическая/комплаенс-проверка
+• Санкционная проверка (кэш CSL США/SDN, ЕС, UK от 04.10.2026): университет не найден; restricted_list пуст
+• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой
+• Перепроверка: Сайты mazust.ac.ir / en.mazust.ac.ir по-прежнему недоступны (04.10.2026, сброс соединения); данные не изменены</t>
         </is>
       </c>
       <c r="AG82" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.usc.ac.ir/
-• Https://en.usc.ac.ir/contact-us/
-• Https://international.usc.ac.ir/en/
-• Https://en.wikipedia.org/wiki/University_of_Science_and_Culture</t>
+          <t>• Https://en.wikipedia.org/wiki/University_of_Science_and_Technology_of_Mazandaran
+• Https://fa.wikipedia.org/wiki/دانشگاه_علم_و_فناوری_مازندران
+• Https://www.mehrnews.com/news/6927510/
+• Https://www.msrt.ir/fa/grid/217/</t>
         </is>
       </c>
       <c r="AH82" s="4" t="inlineStr">
@@ -13300,17 +13394,17 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Бехшехр</t>
+          <t>Урмия</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>University of Science and Technology of Mazandaran</t>
+          <t>Urmia University of Technology (UUT)</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>دانشگاه علم و فناوری مازندران</t>
+          <t>دانشگاه صنعتی ارومیه</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -13325,43 +13419,64 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>• Mathematics
-• Electrical and Computer Engineering
-• Chemical Engineering
-• Industrial Engineering</t>
+          <t>• Electrical engineering
+• Mechanical engineering
+• Civil engineering
+• Chemical engineering
+• Industrial engineering
+• Computer &amp; IT</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>University Blvd., Sea Road, P.O. Box 48518-78195, Behshahr, Mazandaran, Iran</t>
-        </is>
-      </c>
-      <c r="J83" s="4" t="inlineStr"/>
-      <c r="K83" s="4" t="inlineStr"/>
+          <t>Urmia University of Technology, beginning of Band Road, above Golshahr 2, Urmia, West Azerbaijan, Iran (Postal Code 57166-17165)</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>info@uut.ac.ir</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>ФИО не найдено
+Руководитель Управления международных дел
+Общий ящик университета (info@uut.ac.ir)
+Обращение: Dear Director of International Affairs,</t>
+        </is>
+      </c>
       <c r="L83" s="4" t="inlineStr"/>
-      <c r="M83" s="4" t="inlineStr"/>
+      <c r="M83" s="4" t="inlineStr">
+        <is>
+          <t>info@uut.ac.ir</t>
+        </is>
+      </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>+98 11 3455 2008</t>
+          <t>+98 44 3198 0251</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>https://en.mazust.ac.ir</t>
+          <t>https://uut.ac.ir</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>Dr. Ali Tahmasbi</t>
+          <t>Dr. Yaghoub Pourasad</t>
         </is>
       </c>
       <c r="Q83" s="4" t="inlineStr">
         <is>
-          <t>Acting President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="R83" s="4" t="inlineStr"/>
-      <c r="S83" s="4" t="inlineStr"/>
+      <c r="S83" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter (unranked)</t>
+        </is>
+      </c>
       <c r="T83" s="4" t="inlineStr"/>
       <c r="U83" s="4" t="n">
         <v>0</v>
@@ -13380,161 +13495,17 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD83" s="4" t="inlineStr"/>
+      <c r="AD83" s="4" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="AE83" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF83" s="4" t="inlineStr">
-        <is>
-          <t>• Руководитель: д-р Али Тахмасби (прикл. математика) — назначен и.о. президента (Mehr «سرپرست دانشگاه علم و فناوری مازندران منصوب شد», ок. 2026) вместо А. Раббани; статус и.о
-• Не путать с Mazandaran University of Science and Technology (Баболь, ustmb.ac.ir) и University of Mazandaran (umz.ac.ir)
-• E-mail не найден; телефон из сниппета (+98 11 3455 2008) — перепроверить
-• Быстрая проверка спутников: не найдено
-• Иран под всеобъемлющими санкциями США (ITSR/OFAC) и ограничительными мерами ЕС/Великобритании; перед контактом нужна юридическая/комплаенс-проверка
-• Санкционная проверка (кэш CSL США/SDN, ЕС, UK от 04.10.2026): университет не найден; restricted_list пуст
-• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой</t>
-        </is>
-      </c>
-      <c r="AG83" s="4" t="inlineStr">
-        <is>
-          <t>• Https://en.wikipedia.org/wiki/University_of_Science_and_Technology_of_Mazandaran
-• Https://fa.wikipedia.org/wiki/دانشگاه_علم_و_فناوری_مازندران
-• Https://www.mehrnews.com/news/6927510/
-• Https://www.msrt.ir/fa/grid/217/</t>
-        </is>
-      </c>
-      <c r="AH83" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI83" s="4" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>Иран</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>Урмия</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>Urmia University of Technology (UUT)</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>دانشگاه صنعتی ارومیه</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>Технический / аэрокосмический</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>Государственный (Минобрнауки Ирана, MSRT)</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>• Electrical engineering
-• Mechanical engineering
-• Civil engineering
-• Chemical engineering
-• Industrial engineering
-• Computer &amp; IT</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t>Urmia University of Technology, beginning of Band Road, above Golshahr 2, Urmia, West Azerbaijan, Iran (Postal Code 57166-17165)</t>
-        </is>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>info@uut.ac.ir</t>
-        </is>
-      </c>
-      <c r="K84" s="4" t="inlineStr">
-        <is>
-          <t>ФИО не найдено
-Руководитель Управления международных дел
-Общий ящик университета (info@uut.ac.ir)
-Обращение: Dear Director of International Affairs,</t>
-        </is>
-      </c>
-      <c r="L84" s="4" t="inlineStr"/>
-      <c r="M84" s="4" t="inlineStr">
-        <is>
-          <t>info@uut.ac.ir</t>
-        </is>
-      </c>
-      <c r="N84" s="4" t="inlineStr">
-        <is>
-          <t>+98 44 3198 0251</t>
-        </is>
-      </c>
-      <c r="O84" s="4" t="inlineStr">
-        <is>
-          <t>https://uut.ac.ir</t>
-        </is>
-      </c>
-      <c r="P84" s="4" t="inlineStr">
-        <is>
-          <t>Dr. Yaghoub Pourasad</t>
-        </is>
-      </c>
-      <c r="Q84" s="4" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="R84" s="4" t="inlineStr"/>
-      <c r="S84" s="4" t="inlineStr">
-        <is>
-          <t>THE2027: Reporter (unranked)</t>
-        </is>
-      </c>
-      <c r="T84" s="4" t="inlineStr"/>
-      <c r="U84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="4" t="inlineStr"/>
-      <c r="W84" s="4" t="inlineStr"/>
-      <c r="X84" s="4" t="inlineStr"/>
-      <c r="Y84" s="4" t="inlineStr"/>
-      <c r="Z84" s="4" t="inlineStr"/>
-      <c r="AA84" s="4" t="inlineStr"/>
-      <c r="AB84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC84" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD84" s="4" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="AE84" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AF84" s="4" t="inlineStr">
         <is>
           <t>• Прямая связь с президентом: po@uut.ac.ir; личный e-mail президента y.pourasad@uut.ac.ir; тел. приёмной +98 44 3198 0203
 • Подразделение «امور بین الملل» (международные дела) есть, но его страница пуста — e-mail и руководитель не найдены
@@ -13543,7 +13514,7 @@
 • Иран находится под всеобъемлющими санкциями США (ITSR/OFAC) и секторальными санкциями ЕС/Великобритании — любое партнёрство и переписка требуют предварительной юридической (комплаенс) проверки</t>
         </is>
       </c>
-      <c r="AG84" s="4" t="inlineStr">
+      <c r="AG83" s="4" t="inlineStr">
         <is>
           <t>• Https://en.uut.ac.ir/
 • Https://uut.ac.ir/
@@ -13557,48 +13528,48 @@
 • Https://www.nanosats.eu (local export nanosats.csv)</t>
         </is>
       </c>
-      <c r="AH84" s="4" t="inlineStr">
+      <c r="AH83" s="4" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="AI84" s="4" t="inlineStr"/>
+      <c r="AI83" s="4" t="inlineStr"/>
     </row>
-    <row r="85">
-      <c r="A85" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>Иран</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>Ясудж</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>Yasouj University</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>دانشگاه یاسوج</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>Классический</t>
         </is>
       </c>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>Государственный (Минобрнауки Ирана, MSRT)</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>• Agriculture and Natural Resources
 • Engineering
@@ -13607,76 +13578,76 @@
 • Literature</t>
         </is>
       </c>
-      <c r="I85" s="4" t="inlineStr">
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>Daneshjoo St., Yasuj 75918-74934, Kohgiluyeh and Boyer-Ahmad Province, Iran</t>
         </is>
       </c>
-      <c r="J85" s="4" t="inlineStr">
+      <c r="J84" s="4" t="inlineStr">
         <is>
           <t>pr@yu.ac.ir</t>
         </is>
       </c>
-      <c r="K85" s="4" t="inlineStr">
+      <c r="K84" s="4" t="inlineStr">
         <is>
           <t>ФИО не найдено
 Служба по связям с общественностью
 Обращение: Dear Director of International Scientific Cooperation,</t>
         </is>
       </c>
-      <c r="L85" s="4" t="inlineStr"/>
-      <c r="M85" s="4" t="inlineStr">
+      <c r="L84" s="4" t="inlineStr"/>
+      <c r="M84" s="4" t="inlineStr">
         <is>
           <t>pr@yu.ac.ir</t>
         </is>
       </c>
-      <c r="N85" s="4" t="inlineStr"/>
-      <c r="O85" s="4" t="inlineStr">
+      <c r="N84" s="4" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr">
         <is>
           <t>https://yu.ac.ir/en</t>
         </is>
       </c>
-      <c r="P85" s="4" t="inlineStr">
+      <c r="P84" s="4" t="inlineStr">
         <is>
           <t>Dr. Mahdi Nouripour</t>
         </is>
       </c>
-      <c r="Q85" s="4" t="inlineStr">
+      <c r="Q84" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R85" s="4" t="inlineStr"/>
-      <c r="S85" s="4" t="inlineStr"/>
-      <c r="T85" s="4" t="inlineStr"/>
-      <c r="U85" s="4" t="n">
+      <c r="R84" s="4" t="inlineStr"/>
+      <c r="S84" s="4" t="inlineStr"/>
+      <c r="T84" s="4" t="inlineStr"/>
+      <c r="U84" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="4" t="inlineStr"/>
-      <c r="W85" s="4" t="inlineStr"/>
-      <c r="X85" s="4" t="inlineStr"/>
-      <c r="Y85" s="4" t="inlineStr"/>
-      <c r="Z85" s="4" t="inlineStr"/>
-      <c r="AA85" s="4" t="inlineStr"/>
-      <c r="AB85" s="4" t="n">
+      <c r="V84" s="4" t="inlineStr"/>
+      <c r="W84" s="4" t="inlineStr"/>
+      <c r="X84" s="4" t="inlineStr"/>
+      <c r="Y84" s="4" t="inlineStr"/>
+      <c r="Z84" s="4" t="inlineStr"/>
+      <c r="AA84" s="4" t="inlineStr"/>
+      <c r="AB84" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC85" s="7" t="inlineStr">
+      <c r="AC84" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD85" s="4" t="inlineStr">
+      <c r="AD84" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE85" s="4" t="inlineStr">
+      <c r="AE84" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF85" s="4" t="inlineStr">
+      <c r="AF84" s="4" t="inlineStr">
         <is>
           <t>• Президент: д-р Махди Нурипур (fa Wikipedia, сниппет 1404); дата назначения не подтверждена
 • Pr@yu.ac.ir — ящик службы по связям с общественностью (единственный найденный общий адрес); ящик Управления международного научного сотрудничества не найден
@@ -13684,10 +13655,11 @@
 • Быстрая проверка спутников: не найдено
 • Иран под всеобъемлющими санкциями США (ITSR/OFAC) и ограничительными мерами ЕС/Великобритании; перед контактом нужна юридическая/комплаенс-проверка
 • Санкционная проверка (кэш CSL США/SDN, ЕС, UK от 04.10.2026): университет не найден; restricted_list пуст
-• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой</t>
-        </is>
-      </c>
-      <c r="AG85" s="4" t="inlineStr">
+• Официальный сайт (*.ac.ir) недоступен из нашей сети (503/таймаут); контакты взяты из поисковых сниппетов официальных страниц — требуют перепроверки перед рассылкой
+• Перепроверка: 04.10.2026: yu.ac.ir по-прежнему недоступен (503); данные не изменены</t>
+        </is>
+      </c>
+      <c r="AG84" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Yasouj_University
 • Https://fa.wikipedia.org/wiki/دانشگاه_یاسوج
@@ -13695,15 +13667,15 @@
 • Http://president.yu.ac.ir/fa/node/2427</t>
         </is>
       </c>
-      <c r="AH85" s="4" t="inlineStr">
+      <c r="AH84" s="4" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="AI85" s="4" t="inlineStr"/>
+      <c r="AI84" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI85"/>
+  <autoFilter ref="A1:AI84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>